--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20240301_20240901.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20240301_20240901.xlsx
@@ -1185,37 +1185,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.37704918032787</v>
+        <v>56.55737704918032</v>
       </c>
       <c r="C18" t="n">
         <v>42.62295081967213</v>
       </c>
       <c r="D18" t="n">
-        <v>50.59917330241493</v>
+        <v>52.23957588515618</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>INE121J01017</t>
+          <t>INE205A01025</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>-14.75409836065574</v>
+        <v>-13.9344262295082</v>
       </c>
       <c r="H18" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I18" t="n">
         <v>80</v>
       </c>
       <c r="J18" t="n">
-        <v>458.5</v>
+        <v>468.45</v>
       </c>
       <c r="K18" t="n">
         <v>17</v>
@@ -1229,37 +1229,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>56.55737704918032</v>
+        <v>57.37704918032787</v>
       </c>
       <c r="C19" t="n">
         <v>42.62295081967213</v>
       </c>
       <c r="D19" t="n">
-        <v>52.23957588515618</v>
+        <v>50.59917330241493</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>INE205A01025</t>
+          <t>INE121J01017</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>-13.9344262295082</v>
+        <v>-14.75409836065574</v>
       </c>
       <c r="H19" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I19" t="n">
         <v>80</v>
       </c>
       <c r="J19" t="n">
-        <v>468.45</v>
+        <v>458.5</v>
       </c>
       <c r="K19" t="n">
         <v>18</v>
